--- a/public/templates/CITYBUS-BAO-CAO-GPS-BP-QLCL-DV.xlsx
+++ b/public/templates/CITYBUS-BAO-CAO-GPS-BP-QLCL-DV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duykha/Workspace/reactjs/qlcldv/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940DCDAF-A2AC-C846-B58E-D232FFD024B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511ADE98-8AAE-9141-A563-8A66AD05C74F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>BÁO CÁO CÔNG VIỆC TỔNG HỢP TÌNH TRẠNG ĐỊNH VỊ</t>
   </si>
@@ -69,15 +69,6 @@
   </si>
   <si>
     <t>1. BÌNH ANH</t>
-  </si>
-  <si>
-    <t>2. BÌNH ANH 35 TUYẾN</t>
-  </si>
-  <si>
-    <t>3. VIETMAP</t>
-  </si>
-  <si>
-    <t>4. TONGDA</t>
   </si>
   <si>
     <t>5. Khó khăn/đề xuất</t>
@@ -101,6 +92,12 @@
   </si>
   <si>
     <t xml:space="preserve">Họ &amp; Tên: </t>
+  </si>
+  <si>
+    <t>2. VIETMAP</t>
+  </si>
+  <si>
+    <t>3. TONGDA</t>
   </si>
 </sst>
 </file>
@@ -289,7 +286,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -309,9 +306,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -330,32 +324,29 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -656,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -669,71 +660,71 @@
     <col min="10" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-    </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="15" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+    </row>
+    <row r="5" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:6" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-    </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+    </row>
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
       <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
@@ -747,11 +738,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="11"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="6">
         <v>0</v>
       </c>
@@ -765,57 +756,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="10">
+      <c r="B9" s="20"/>
+      <c r="C9" s="9">
         <f>SUM(C8:C8)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <f>SUM(D8:D8)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <f>SUM(E8:E8)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <f>SUM(F8:F8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16" t="s">
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
       <c r="C12" s="2" t="s">
         <v>4</v>
       </c>
@@ -828,9 +817,8 @@
       <c r="F12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -841,63 +829,62 @@
       <c r="D13" s="6">
         <v>0</v>
       </c>
-      <c r="E13" s="6">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="17" t="s">
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10">
-        <f>SUM(C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
-        <f t="shared" ref="D14:F14" si="0">SUM(D13)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-    </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="16" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="9">
+        <f>SUM(C13:C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <f>SUM(D13:D13)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <f>SUM(E13:E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <f>SUM(F13:F13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+    </row>
+    <row r="16" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-    </row>
-    <row r="17" spans="1:6" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+    </row>
+    <row r="17" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="2" t="s">
         <v>4</v>
       </c>
@@ -911,130 +898,94 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="12"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="6">
         <v>0</v>
       </c>
       <c r="D18" s="6">
         <v>0</v>
       </c>
-      <c r="E18" s="5">
-        <v>0</v>
-      </c>
-      <c r="F18" s="5">
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="10">
-        <f>SUM(C18:C18)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="10">
-        <f>SUM(D18:D18)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="10">
-        <f>SUM(E18:E18)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="10">
-        <f>SUM(F18:F18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-    </row>
-    <row r="21" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="4">
-        <v>1</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="6">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="9">
-        <f>SUM(C23)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="9">
-        <f t="shared" ref="D24:F24" si="1">SUM(D23)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="15" t="s">
-        <v>15</v>
-      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="8">
+        <f>SUM(C18)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" ref="D19:F19" si="0">SUM(D18)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+    </row>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -1042,93 +993,44 @@
       <c r="F25" s="15"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A26:C32"/>
-    <mergeCell ref="D26:F32"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
+  <mergeCells count="21">
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A21:C27"/>
+    <mergeCell ref="D21:F27"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
